--- a/workbook/Chaos_Engineering_Scenario_Catalog_v2.xlsx
+++ b/workbook/Chaos_Engineering_Scenario_Catalog_v2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Service Inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Scenario Catalog" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Priority Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Wave Plan" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Coverage Matrix" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Open Items" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="App Scan Instructions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Infra Scan Instructions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service Inventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Catalog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Matrix" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Items" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Scan Instructions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Scan Instructions" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Service Inventory'!$A$1:$N$18</definedName>
@@ -721,7 +721,7 @@
     <row r="2" ht="15" customHeight="1" s="19">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Audience: Sr. technical leadership (program review) and the Chaos Engineering team (execution). Derived from code-based assessment artifacts, C1–C4/SVC-AB diagrams, the recon (SVC-P) pipeline diagram/narrative, and prior FMEA / timeout-chain / DR work. Nothing in the catalog is invented beyond those sources; unknowns are flagged in Open Items.</t>
+          <t>Audience: Sr. technical leadership (program review) and the Chaos Engineering team (execution). Derived from code-based assessment artifacts, C1–C4/EAC diagrams, the recon (DTR) pipeline diagram/narrative, and prior FMEA / timeout-chain / DR work. Nothing in the catalog is invented beyond those sources; unknowns are flagged in Open Items.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Every scenario has TWO pass conditions: the system behaved as hypothesized AND the fault was detected/alerted correctly (APM-platform + CloudWatch). A fault that recovers silently is a FAILED experiment. Detection baseline scenarios (CE-OBS-*) run in Wave 1 for this reason.</t>
+          <t>Every scenario has TWO pass conditions: the system behaved as hypothesized AND the fault was detected/alerted correctly (Dynatrace + CloudWatch). A fault that recovers silently is a FAILED experiment. Detection baseline scenarios (CE-OBS-*) run in Wave 1 for this reason.</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Accts Lookup Component</t>
+          <t>Account Locator Component</t>
         </is>
       </c>
       <c r="C2" s="27" t="inlineStr">
         <is>
-          <t>APP-A</t>
+          <t>ALS</t>
         </is>
       </c>
       <c r="D2" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-4</t>
+          <t>LOCR</t>
         </is>
       </c>
       <c r="E2" s="27" t="inlineStr">
@@ -1100,17 +1100,17 @@
       </c>
       <c r="J2" s="27" t="inlineStr">
         <is>
-          <t>SVC-F (Register)</t>
+          <t>ACL (Register)</t>
         </is>
       </c>
       <c r="K2" s="27" t="inlineStr">
         <is>
-          <t>Inbound only (EXT-2/SVC-U/SVC-V/SVC-T/Payments/SVC-Y/SVC-X)</t>
+          <t>Inbound only (ARR/FAP/DCPA/DCP/Payments/SPG/OCS)</t>
         </is>
       </c>
       <c r="L2" s="27" t="inlineStr">
         <is>
-          <t>Prod: Lookup Event→broker→Datalake; Batch: Lambda→S3→managed-file-transfer→upstream-feed</t>
+          <t>Prod: Locator Event→MBUS→Datalake; Batch: Lambda→S3→MFT→EDX</t>
         </is>
       </c>
       <c r="M2" s="27" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>SVC-B</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-1</t>
+          <t>ACCT</t>
         </is>
       </c>
       <c r="E3" s="27" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J3" s="27" t="inlineStr">
         <is>
-          <t>Inbound only (SVC-C/SVC-D/SVC-M/SVC-N/SVC-G/SVC-L)</t>
+          <t>Inbound only (SAM/AFM/DBE/DTE/DSM/DCM)</t>
         </is>
       </c>
       <c r="K3" s="27" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>SVC-C</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-1</t>
+          <t>ACCT</t>
         </is>
       </c>
       <c r="E4" s="27" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="G4" s="27" t="inlineStr">
         <is>
-          <t>R53→NLB→API GW→NLB→ALB→ECS (from LOB-1/EXT-2)</t>
+          <t>R53→NLB→API GW→NLB→ALB→ECS (from SMB/ARR)</t>
         </is>
       </c>
       <c r="H4" s="27" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="J4" s="27" t="inlineStr">
         <is>
-          <t>APP-A, SVC-B, SVC-D, SVC-F</t>
+          <t>ALS, ARM, AFM, ACL</t>
         </is>
       </c>
       <c r="K4" s="27" t="inlineStr">
         <is>
-          <t>EXT (Account Mgmt)</t>
+          <t>CBS (Account Mgmt)</t>
         </is>
       </c>
       <c r="L4" s="27" t="inlineStr">
         <is>
-          <t>Prod: Core Acct Change→broker→Datalake; Cons: broker incl. APP-GRP-6 EOD Completion</t>
+          <t>Prod: Core Acct Change→MBUS→Datalake; Cons: MBUS incl. RECN EOD Completion</t>
         </is>
       </c>
       <c r="M4" s="27" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>SVC-D</t>
+          <t>AFM</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-1</t>
+          <t>ACCT</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>R53→NLB→API GW→NLB→ALB→ECS (from SVC-C)</t>
+          <t>R53→NLB→API GW→NLB→ALB→ECS (from SAM)</t>
         </is>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>Aurora (direct — SVC-D DB), ElastiCache</t>
+          <t>Aurora (direct — AFM DB), ElastiCache</t>
         </is>
       </c>
       <c r="I5" s="27" t="inlineStr">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="J5" s="27" t="inlineStr">
         <is>
-          <t>REFDATA, SVC-M, SVC-G, SVC-L, SVC-B, SVC-F</t>
+          <t>MCC, DBE, DSM, DCM, ARM, ACL</t>
         </is>
       </c>
       <c r="K5" s="27" t="inlineStr">
         <is>
-          <t>EXT Posting, EXT Transaction</t>
+          <t>CBS Posting, CBS Transaction</t>
         </is>
       </c>
       <c r="L5" s="27" t="inlineStr">
         <is>
-          <t>Prod: Feature State Change→broker (→SVC-T, Datalake)</t>
+          <t>Prod: Feature State Change→MBUS (→DCP-TA, Datalake)</t>
         </is>
       </c>
       <c r="M5" s="27" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Accts Lookup Admin Tool</t>
+          <t>Account Locator Admin Tool</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>SVC-E</t>
+          <t>DLAT</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-4</t>
+          <t>LOCR</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>SVC-F</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-1</t>
+          <t>ACCT</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="J7" s="27" t="inlineStr">
         <is>
-          <t>Receives SVC-C/SVC-D/APP-A registrations</t>
+          <t>Receives SAM/AFM/ALS registrations</t>
         </is>
       </c>
       <c r="K7" s="27" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="L7" s="27" t="inlineStr">
         <is>
-          <t>Cons: Core Acct Change, Feature Change (SVC-C/SVC-D/APP-A)</t>
+          <t>Cons: Core Acct Change, Feature Change (SAM/AFM/ALS)</t>
         </is>
       </c>
       <c r="M7" s="27" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Accts Ledger Management</t>
+          <t>Core Subledger Management</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>SVC-G</t>
+          <t>DSM</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-2</t>
+          <t>REFD</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="J8" s="27" t="inlineStr">
         <is>
-          <t>REFDATA, SVC-B (migration lookup)</t>
+          <t>MCC, ARM (migration lookup)</t>
         </is>
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
-          <t>EXT (Ledger+RoutingRule, Balance Inquiry), Payments/SVC-W</t>
+          <t>CBS (Subledger+RoutingRule, Balance Inquiry), Payments/MMS</t>
         </is>
       </c>
       <c r="L8" s="27" t="inlineStr">
         <is>
-          <t>Prod: Ledger CUD→broker→EXT-3+Continuum/DataLake; +Migration Topic</t>
+          <t>Prod: Subledger CUD→MBUS→AU+Continuum/DataLake; +Migration Topic</t>
         </is>
       </c>
       <c r="M8" s="27" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Spend &amp; Save Experience Svc</t>
+          <t>Spend-Track Experience Svc</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>SVC-H</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-2</t>
+          <t>REFD</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>SVC-I</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-3</t>
+          <t>ENRC</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>Via edge-proxy/Digital; shares org-REDACTED ingress</t>
+          <t>Via DPS Proxy/Digital; shares 900069 ingress</t>
         </is>
       </c>
       <c r="H10" s="27" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="J10" s="27" t="inlineStr">
         <is>
-          <t>SVC-L (Chore Inquiry for notifications), REFDATA (Spend Categories)</t>
+          <t>DCM (Task Inquiry for Nudges), MCC (Spend Categories)</t>
         </is>
       </c>
       <c r="K10" s="27" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>SVC-J</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-5</t>
+          <t>ALRT</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t>CDN→edge-gateway→edge-proxy→transit-gateway→R53→API GW (SSO-anywhere token validate)→NLB→ALB→ECS</t>
+          <t>Akamai→CTC→DPS Proxy→Transit GW→R53→API GW (AuthAnywhere token validate)→NLB→ALB→ECS</t>
         </is>
       </c>
       <c r="H11" s="27" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="K11" s="27" t="inlineStr">
         <is>
-          <t>context-service, SVC-R/SVC-R2 Transactions, onprem-broker on-prem via service-mesh, SSO-anywhere</t>
+          <t>ChannelContext, ETU/TU Transactions, GKP on-prem via Envoy, AuthAnywhere</t>
         </is>
       </c>
       <c r="L11" s="27" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>REFDATA Data Management Svc</t>
+          <t>MCC Data Management Svc</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>REFDATA</t>
+          <t>MCC</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-2</t>
+          <t>REFD</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>API GW→NLB→ALB→ECS (+ On-Prem API GW); EventBridge scheduler (SVC-R pull)</t>
+          <t>API GW→NLB→ALB→ECS (+ On-Prem API GW); EventBridge scheduler (ETU pull)</t>
         </is>
       </c>
       <c r="H12" s="27" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="J12" s="27" t="inlineStr">
         <is>
-          <t>Inbound only (SVC-G, SVC-C/Acct Creation, Tasks Exp)</t>
+          <t>Inbound only (DSM, SAM/Acct Creation, Tasks Exp)</t>
         </is>
       </c>
       <c r="K12" s="27" t="inlineStr">
         <is>
-          <t>SVC-R (GET Reference Data, scheduled)</t>
+          <t>ETU (GET Reference Data, scheduled)</t>
         </is>
       </c>
       <c r="L12" s="27" t="inlineStr">
         <is>
-          <t>Scheduler-triggered SVC-R pull; writes config→S3; no Kafka publish</t>
+          <t>Scheduler-triggered ETU pull; writes config→S3; no Kafka publish</t>
         </is>
       </c>
       <c r="M12" s="27" t="inlineStr">
         <is>
-          <t>EventBridge SVC-R pull</t>
+          <t>EventBridge ETU pull</t>
         </is>
       </c>
       <c r="N12" s="27" t="inlineStr">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Accts Chore Management</t>
+          <t>Core Task Management</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>SVC-L</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-3</t>
+          <t>ENRC</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>Via edge-proxy/Digital &amp; Payments-platform→NLB→NLB→ALB (+API GW Regional Endpt); weekly-job scheduler via SQS</t>
+          <t>Via DPS Proxy/Digital &amp; Banking Payments→NLB→NLB→ALB (+API GW Regional Endpt); weekly-job scheduler via SQS</t>
         </is>
       </c>
       <c r="H13" s="27" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="J13" s="27" t="inlineStr">
         <is>
-          <t>SVC-B, SVC-C, Acct Alerts (SVC-AA org-REDACTED)</t>
+          <t>ARM, SAM, Core Alerts (DCC 900070)</t>
         </is>
       </c>
       <c r="K13" s="27" t="inlineStr">
         <is>
-          <t>EXT (posting/balance inquiry via Digital Payments)</t>
+          <t>CBS (posting/balance inquiry via Digital Payments)</t>
         </is>
       </c>
       <c r="L13" s="27" t="inlineStr">
         <is>
-          <t>Prod: Chore Life Cycle→broker (→Alerts, SVC-N); SQS: weekly future-chore job</t>
+          <t>Prod: Task Life Cycle→MBUS (→Alerts, DTE); SQS: weekly future-task job</t>
         </is>
       </c>
       <c r="M13" s="27" t="inlineStr">
@@ -1900,17 +1900,17 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>Accts Balance Enrichment</t>
+          <t>Core Balance Enrichment</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>SVC-M</t>
+          <t>DBE</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-3</t>
+          <t>ENRC</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>Kafka EXT Balance Changed; + API (API GW→NLB→ALB)</t>
+          <t>Kafka (MBUS) CBS Balance Changed; + API (API GW→NLB→ALB)</t>
         </is>
       </c>
       <c r="H14" s="27" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="J14" s="27" t="inlineStr">
         <is>
-          <t>SVC-B (acct identifier), SVC-G (Ledger Inquiry — cache-miss fallback)</t>
+          <t>ARM (acct identifier), DSM (Subledger Inquiry — cache-miss fallback)</t>
         </is>
       </c>
       <c r="K14" s="27" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="L14" s="27" t="inlineStr">
         <is>
-          <t>Cons: EXT Balance Changed. Prod: Enriched Sub-Ledger Balance Updated→broker→EXT-3</t>
+          <t>Cons: CBS Balance Changed. Prod: Enriched Sub-Ledger Balance Updated→MBUS→AU</t>
         </is>
       </c>
       <c r="M14" s="27" t="inlineStr">
@@ -1970,22 +1970,22 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Accts Transaction Enrichment</t>
+          <t>Core Transaction Enrichment</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>SVC-N</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-3</t>
+          <t>ENRC</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Event processor + Data-Quality/Ledger-Txn API — mixed</t>
+          <t>Event processor + Data-Quality/Subledger-Txn API — mixed</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>Kafka EXT Transaction Events; + API (API GW→NLB→ALB)</t>
+          <t>Kafka (MBUS) CBS Transaction Events; + API (API GW→NLB→ALB)</t>
         </is>
       </c>
       <c r="H15" s="27" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="J15" s="27" t="inlineStr">
         <is>
-          <t>SVC-B, SVC-G (fallback), Chore Svc (Get Chore Name)</t>
+          <t>ARM, DSM (fallback), Task Svc (Get Task Name)</t>
         </is>
       </c>
       <c r="K15" s="27" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="L15" s="27" t="inlineStr">
         <is>
-          <t>Cons: EXT Transaction Events. Prod: Enriched Sub-Ledger Txn→broker→SVC-R</t>
+          <t>Cons: CBS Transaction Events. Prod: Enriched Sub-Ledger Txn→MBUS→ETU</t>
         </is>
       </c>
       <c r="M15" s="27" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Accts Sub Ledger Data Consumer</t>
+          <t>Core Sub Ledger Data Consumer</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>SVC-O</t>
+          <t>DSC</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-3</t>
+          <t>ENRC</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t>Kafka Ledger CUD / Partition Lifecycle (from SVC-G)</t>
+          <t>Kafka (MBUS) Subledger CUD / Partition Lifecycle (from DSM)</t>
         </is>
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>ElastiCache (writes ledger type/name), Aurora (shared cluster/own schema)</t>
+          <t>ElastiCache (writes subledger type/name), Aurora (shared cluster/own schema)</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="L16" s="27" t="inlineStr">
         <is>
-          <t>Cons: Ledger CUD/Lifecycle. Prod: none</t>
+          <t>Cons: Subledger CUD/Lifecycle. Prod: none</t>
         </is>
       </c>
       <c r="M16" s="27" t="inlineStr">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Accts Transaction Recon</t>
+          <t>Core Transaction Recon</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-6</t>
+          <t>RECN</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="G17" s="27" t="inlineStr">
         <is>
-          <t>file/managed-file-transfer (upstream-feed RDF/ADF/CDF→S3→SQS→Lambda); EventBridge scheduler; Kafka EXT EOD Completion</t>
+          <t>file/MFT (EDX RDF/ADF/CDF→S3→SQS→Lambda); EventBridge scheduler; Kafka CBS EOD Completion</t>
         </is>
       </c>
       <c r="H17" s="27" t="inlineStr">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="J17" s="27" t="inlineStr">
         <is>
-          <t>Accts Transaction Svc (Txn Inquiry — SOR fallback)</t>
+          <t>Core Transaction Svc (Txn Inquiry — SOR fallback)</t>
         </is>
       </c>
       <c r="K17" s="27" t="inlineStr">
         <is>
-          <t>EXT (EOD Txn Inquiry, Posting API for corrections), upstream-feed (email)</t>
+          <t>CBS (EOD Txn Inquiry, Posting API for corrections), EDX (email)</t>
         </is>
       </c>
       <c r="L17" s="27" t="inlineStr">
         <is>
-          <t>Cons: EXT EOD Completion + Balance/Txn CUD. Prod: Bankwise Recon Completion→Acct Closure (SVC-C), Recon Event; SQS/SNS/Lambda</t>
+          <t>Cons: CBS EOD Completion + Balance/Txn CUD. Prod: Bankwise Recon Completion→Acct Closure (SAM), Recon Event; SQS/SNS/Lambda</t>
         </is>
       </c>
       <c r="M17" s="27" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Acct Alerts</t>
+          <t>Core Alerts</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>SVC-Q</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-5</t>
+          <t>ALRT</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G18" s="27" t="inlineStr">
         <is>
-          <t>Kafka (Enriched Txn CUD, Chore Lifecycle, channel-alert Topic) + API; CRON scheduler (failure recovery); API GW/NLB/ALB/R53</t>
+          <t>Kafka (Enriched Txn CUD, Task Lifecycle, D2 Alert Topic) + API; CRON scheduler (failure recovery); API GW/NLB/ALB/R53</t>
         </is>
       </c>
       <c r="H18" s="27" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="K18" s="27" t="inlineStr">
         <is>
-          <t>CUST (Fetch Parent/Child, payload enrichment)</t>
+          <t>CSU (Fetch Parent/Child, payload enrichment)</t>
         </is>
       </c>
       <c r="L18" s="27" t="inlineStr">
         <is>
-          <t>Cons: Enriched Txn CUD + Chore Lifecycle. Prod: enriched alerts→SVC-AC Alert Topic→SVC-AC</t>
+          <t>Cons: Enriched Txn CUD + Task Lifecycle. Prod: enriched alerts→Notify Alert Topic→NOTIFY</t>
         </is>
       </c>
       <c r="M18" s="27" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F2" s="27" t="inlineStr">
         <is>
-          <t>SVC-C (repeat per sync API)</t>
+          <t>SAM (repeat per sync API)</t>
         </is>
       </c>
       <c r="G2" s="27" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M2" s="27" t="inlineStr">
         <is>
-          <t>APM-platform detects task churn; no false-positive paging for single-task events (noise calibration).</t>
+          <t>Dynatrace detects task churn; no false-positive paging for single-task events (noise calibration).</t>
         </is>
       </c>
       <c r="N2" s="27" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F3" s="27" t="inlineStr">
         <is>
-          <t>SVC-B, SVC-C</t>
+          <t>ARM, SAM</t>
         </is>
       </c>
       <c r="G3" s="27" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M3" s="27" t="inlineStr">
         <is>
-          <t>Capacity alarm fires; APM-platform shows saturation before errors.</t>
+          <t>Capacity alarm fires; Dynatrace shows saturation before errors.</t>
         </is>
       </c>
       <c r="N3" s="27" t="inlineStr">
@@ -2774,17 +2774,17 @@
       </c>
       <c r="F5" s="27" t="inlineStr">
         <is>
-          <t>SVC-M, SVC-N</t>
+          <t>DBE, DTE</t>
         </is>
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>Kill a consumer task while it processes a batch of EXT events.</t>
+          <t>Kill a consumer task while it processes a batch of CBS events.</t>
         </is>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>Offsets uncommitted messages are redelivered; enrichment is idempotent — no lost and no duplicate enriched events downstream (EXT-3/SVC-R).</t>
+          <t>Offsets uncommitted messages are redelivered; enrichment is idempotent — no lost and no duplicate enriched events downstream (AU/ETU).</t>
         </is>
       </c>
       <c r="I5" s="27" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="M5" s="27" t="inlineStr">
         <is>
-          <t>Lag + rebalance visible in APM-platform; DLQ/poison alarms silent.</t>
+          <t>Lag + rebalance visible in Dynatrace; DLQ/poison alarms silent.</t>
         </is>
       </c>
       <c r="N5" s="27" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>SVC-G task recycle — in-memory hashmap loss</t>
+          <t>DSM task recycle — in-memory hashmap loss</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="F6" s="27" t="inlineStr">
         <is>
-          <t>SVC-G (+SVC-O warmer)</t>
+          <t>DSM (+DSC warmer)</t>
         </is>
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>Recycle SVC-G tasks; measure window where in-memory ledger map is cold before SVC-O/ElastiCache warm state is usable.</t>
+          <t>Recycle DSM tasks; measure window where in-memory subledger map is cold before DSC/ElastiCache warm state is usable.</t>
         </is>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
-          <t>SVC-G serves correct responses during warm-up (falls back to Aurora/ElastiCache) with bounded latency penalty; no wrong answers from empty map.</t>
+          <t>DSM serves correct responses during warm-up (falls back to Aurora/ElastiCache) with bounded latency penalty; no wrong answers from empty map.</t>
         </is>
       </c>
       <c r="I6" s="27" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="J6" s="27" t="inlineStr">
         <is>
-          <t>SVC-G only</t>
+          <t>DSM only</t>
         </is>
       </c>
       <c r="K6" s="27" t="inlineStr">
         <is>
-          <t>Incorrect ledger responses</t>
+          <t>Incorrect subledger responses</t>
         </is>
       </c>
       <c r="L6" s="27" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M6" s="27" t="inlineStr">
         <is>
-          <t>Warm-up window observable as metric; SVC-O warmer health alarmed.</t>
+          <t>Warm-up window observable as metric; DSC warmer health alarmed.</t>
         </is>
       </c>
       <c r="N6" s="27" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="F9" s="27" t="inlineStr">
         <is>
-          <t>SVC-L weekly job, REFDATA SVC-R pull, SVC-Q cron</t>
+          <t>DCM weekly job, MCC ETU pull, DAL cron</t>
         </is>
       </c>
       <c r="G9" s="27" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="L9" s="27" t="inlineStr">
         <is>
-          <t>No duplicate chore-job effects / double SVC-R pull / double alert recovery; missed-window path defined.</t>
+          <t>No duplicate task-job effects / double ETU pull / double alert recovery; missed-window path defined.</t>
         </is>
       </c>
       <c r="M9" s="27" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>Mixed (APP-GRP-3)</t>
+          <t>Mixed (ENRC)</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>SVC-L, SVC-M, SVC-N</t>
+          <t>DCM, DBE, DTE</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J10" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-3 cluster</t>
+          <t>ENRC cluster</t>
         </is>
       </c>
       <c r="K10" s="27" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="M10" s="27" t="inlineStr">
         <is>
-          <t>DB failover event alarmed; APM-platform DB-layer signal correct.</t>
+          <t>DB failover event alarmed; Dynatrace DB-layer signal correct.</t>
         </is>
       </c>
       <c r="N10" s="27" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="F11" s="27" t="inlineStr">
         <is>
-          <t>SVC-C (Core DB)</t>
+          <t>SAM (Core DB)</t>
         </is>
       </c>
       <c r="G11" s="27" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>SVC-C + heaviest callers</t>
+          <t>SAM + heaviest callers</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Proxy-fronted APP-GRP-3 services</t>
+          <t>Proxy-fronted ENRC services</t>
         </is>
       </c>
       <c r="G13" s="27" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="H14" s="27" t="inlineStr">
         <is>
-          <t>Services and DR runbooks tolerate documented lag; RPO assumptions (incl. SVC-M 'RPO PoF') hold under stress.</t>
+          <t>Services and DR runbooks tolerate documented lag; RPO assumptions (incl. DBE 'RPO PoF') hold under stress.</t>
         </is>
       </c>
       <c r="I14" s="27" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Mixed (APP-GRP-3)</t>
+          <t>Mixed (ENRC)</t>
         </is>
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
-          <t>SVC-L, SVC-M, SVC-N</t>
+          <t>DCM, DBE, DTE</t>
         </is>
       </c>
       <c r="G19" s="27" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="H19" s="27" t="inlineStr">
         <is>
-          <t>Services fail fast per timeout chain (no hang); recovery on restore without restart; proxy-as-SPOF risk quantified for the 3 APP-GRP-3 services.</t>
+          <t>Services fail fast per timeout chain (no hang); recovery on restore without restart; proxy-as-SPOF risk quantified for the 3 ENRC services.</t>
         </is>
       </c>
       <c r="I19" s="27" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="J19" s="27" t="inlineStr">
         <is>
-          <t>APP-GRP-3 DB access</t>
+          <t>ENRC DB access</t>
         </is>
       </c>
       <c r="K19" s="27" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Shared cluster users (SVC-B, SVC-D, SVC-M, SVC-N, SVC-L)</t>
+          <t>Shared cluster users (ARM, AFM, DBE, DTE, DCM)</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="F21" s="27" t="inlineStr">
         <is>
-          <t>SVC-B, SVC-D (cache-dependent APIs)</t>
+          <t>ARM, AFM (cache-dependent APIs)</t>
         </is>
       </c>
       <c r="G21" s="27" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Cache auth token retrieval failure (secrets-manager)</t>
+          <t>Cache auth token retrieval failure (VaultSM ASM)</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>Deny secrets-mgr secret retrieval for Redis auth token; include a task recycle during the outage.</t>
+          <t>Deny ASM secret retrieval for Redis auth token; include a task recycle during the outage.</t>
         </is>
       </c>
       <c r="H22" s="27" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>Custom (secrets-mgr deny in PERF)</t>
+          <t>Custom (ASM deny in PERF)</t>
         </is>
       </c>
       <c r="J22" s="27" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F23" s="27" t="inlineStr">
         <is>
-          <t>SVC-B/SVC-D + Aurora</t>
+          <t>ARM/AFM + Aurora</t>
         </is>
       </c>
       <c r="G23" s="27" t="inlineStr">
@@ -4828,17 +4828,17 @@
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
-          <t>Fail Redis while SVC-P is mid-reconciliation (EOD txn cache in use).</t>
+          <t>Fail Redis while DTR is mid-reconciliation (EOD txn cache in use).</t>
         </is>
       </c>
       <c r="H24" s="27" t="inlineStr">
         <is>
-          <t>Recon detects datastore loss, fails safe (no partial/incorrect postings), and is restartable — re-pull from EXT EOD API rather than corrupt continuation.</t>
+          <t>Recon detects datastore loss, fails safe (no partial/incorrect postings), and is restartable — re-pull from CBS EOD API rather than corrupt continuation.</t>
         </is>
       </c>
       <c r="I24" s="27" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="F25" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="G25" s="27" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>broker cluster unreachable</t>
+          <t>MBUS cluster unreachable</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F27" s="27" t="inlineStr">
         <is>
-          <t>SVC-M, SVC-N, SVC-O, SVC-Q, SVC-G, SVC-C, SVC-L, SVC-D</t>
+          <t>DBE, DTE, DSC, DAL, DSM, SAM, DCM, AFM</t>
         </is>
       </c>
       <c r="G27" s="27" t="inlineStr">
         <is>
-          <t>Blackhole network path to on-prem broker (dc-1/dc-2).</t>
+          <t>Blackhole network path to on-prem MBUS (C001/C002).</t>
         </is>
       </c>
       <c r="H27" s="27" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>broker unreachable during EOD window</t>
+          <t>MBUS unreachable during EOD window</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
@@ -5264,17 +5264,17 @@
       </c>
       <c r="F28" s="27" t="inlineStr">
         <is>
-          <t>SVC-P primarily</t>
+          <t>DTR primarily</t>
         </is>
       </c>
       <c r="G28" s="27" t="inlineStr">
         <is>
-          <t>broker outage timed across EXT EOD Completion publication.</t>
+          <t>MBUS outage timed across CBS EOD Completion publication.</t>
         </is>
       </c>
       <c r="H28" s="27" t="inlineStr">
         <is>
-          <t>SVC-P's missing-trigger handling (see PIPE-06) engages; recon completes late-but-correct via defined recovery, inside business tolerance.</t>
+          <t>DTR's missing-trigger handling (see PIPE-06) engages; recon completes late-but-correct via defined recovery, inside business tolerance.</t>
         </is>
       </c>
       <c r="I28" s="27" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L28" s="27" t="inlineStr">
         <is>
-          <t>Recovery path exercised end-to-end; late-recon comms path (upstream-feed/Ops) fires.</t>
+          <t>Recovery path exercised end-to-end; late-recon comms path (EDX/Ops) fires.</t>
         </is>
       </c>
       <c r="M28" s="27" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>SVC-M or SVC-N</t>
+          <t>DBE or DTE</t>
         </is>
       </c>
       <c r="G29" s="27" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="F30" s="27" t="inlineStr">
         <is>
-          <t>SVC-M, SVC-N, SVC-O, SVC-Q (each)</t>
+          <t>DBE, DTE, DSC, DAL (each)</t>
         </is>
       </c>
       <c r="G30" s="27" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="F31" s="27" t="inlineStr">
         <is>
-          <t>SVC-M, SVC-N, SVC-O, SVC-Q (each)</t>
+          <t>DBE, DTE, DSC, DAL (each)</t>
         </is>
       </c>
       <c r="G31" s="27" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="H31" s="27" t="inlineStr">
         <is>
-          <t>Every consumer is effectively idempotent: no duplicate enriched events to EXT-3/SVC-R, no duplicate alerts to SVC-AC, no double cache writes.</t>
+          <t>Every consumer is effectively idempotent: no duplicate enriched events to AU/ETU, no duplicate alerts to NOTIFY, no double cache writes.</t>
         </is>
       </c>
       <c r="I31" s="27" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>SVC-M, SVC-N</t>
+          <t>DBE, DTE</t>
         </is>
       </c>
       <c r="G32" s="27" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H32" s="27" t="inlineStr">
         <is>
-          <t>Backlog drains within recovery-time model; ordering preserved; downstream (EXT-3/SVC-R) absorbs burst.</t>
+          <t>Backlog drains within recovery-time model; ordering preserved; downstream (AU/ETU) absorbs burst.</t>
         </is>
       </c>
       <c r="I32" s="27" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>IdP OAUTHBEARER token failure (Kafka auth)</t>
+          <t>IDP OAUTHBEARER token failure (Kafka auth)</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -5807,17 +5807,17 @@
       </c>
       <c r="G33" s="27" t="inlineStr">
         <is>
-          <t>Block IdP token issuance for Kafka SASL auth; include re-auth boundary.</t>
+          <t>Block IDP token issuance for Kafka SASL auth; include re-auth boundary.</t>
         </is>
       </c>
       <c r="H33" s="27" t="inlineStr">
         <is>
-          <t>Existing sessions survive to re-auth boundary; failed re-auth backs off sanely (no auth-storm against IdP); clear failure signature.</t>
+          <t>Existing sessions survive to re-auth boundary; failed re-auth backs off sanely (no auth-storm against IDP); clear failure signature.</t>
         </is>
       </c>
       <c r="I33" s="27" t="inlineStr">
         <is>
-          <t>Custom (Token-provider path block PERF)</t>
+          <t>Custom (IDP path block PERF)</t>
         </is>
       </c>
       <c r="J33" s="27" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>SVC-G, SVC-M (ledger/balance event aliases)</t>
+          <t>DSM, DBE (subledger/balance event aliases)</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>SVC-P + upstream-feed path</t>
+          <t>DTR + EDX path</t>
         </is>
       </c>
       <c r="G36" s="27" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H36" s="27" t="inlineStr">
         <is>
-          <t>EventBridge SLA validator detects absence at cutoff and upstream-feed email notification fires (narrative step 2a); recon for other banks proceeds unaffected.</t>
+          <t>EventBridge SLA validator detects absence at cutoff and EDX email notification fires (narrative step 2a); recon for other banks proceeds unaffected.</t>
         </is>
       </c>
       <c r="I36" s="27" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>SVC-P (Lambda validate/parse)</t>
+          <t>DTR (Lambda validate/parse)</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>Validation Lambda rejects cleanly; rejection reaches Ops/upstream-feed; no partial ingestion poisons downstream SQS.</t>
+          <t>Validation Lambda rejects cleanly; rejection reaches Ops/EDX; no partial ingestion poisons downstream SQS.</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="F38" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="G38" s="27" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>SVC-P chunking Lambda</t>
+          <t>DTR chunking Lambda</t>
         </is>
       </c>
       <c r="G39" s="27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="F40" s="27" t="inlineStr">
         <is>
-          <t>SVC-P queues (+ SVC-L weekly-job queue)</t>
+          <t>DTR queues (+ DCM weekly-job queue)</t>
         </is>
       </c>
       <c r="G40" s="27" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Dual-trigger failure A: files present, EXT EOD event absent</t>
+          <t>Dual-trigger failure A: files present, CBS EOD event absent</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="G41" s="27" t="inlineStr">
         <is>
-          <t>Deliver files normally; suppress EXT EOD Completion event.</t>
+          <t>Deliver files normally; suppress CBS EOD Completion event.</t>
         </is>
       </c>
       <c r="H41" s="27" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="F42" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="G42" s="27" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>SVC-P EventBridge</t>
+          <t>DTR EventBridge</t>
         </is>
       </c>
       <c r="G43" s="27" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="F44" s="27" t="inlineStr">
         <is>
-          <t>SVC-P buckets</t>
+          <t>DTR buckets</t>
         </is>
       </c>
       <c r="G44" s="27" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="J45" s="27" t="inlineStr">
         <is>
-          <t>Recon run + EXT postings</t>
+          <t>Recon run + CBS postings</t>
         </is>
       </c>
       <c r="K45" s="27" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="O45" s="27" t="inlineStr">
         <is>
-          <t>Logic-level; PERF EXT dedicated instance receives corrections — confirm reversibility.</t>
+          <t>Logic-level; PERF CBS dedicated instance receives corrections — confirm reversibility.</t>
         </is>
       </c>
       <c r="P45" s="27" t="n">
@@ -7188,17 +7188,17 @@
       </c>
       <c r="F46" s="27" t="inlineStr">
         <is>
-          <t>SVC-P + Accts Transaction Svc</t>
+          <t>DTR + Core Transaction Svc</t>
         </is>
       </c>
       <c r="G46" s="27" t="inlineStr">
         <is>
-          <t>Engineer EOD dataset gaps so lookups miss (SVC-AD/EXT cutoff skew per narrative 5a).</t>
+          <t>Engineer EOD dataset gaps so lookups miss (LCDP/CBS cutoff skew per narrative 5a).</t>
         </is>
       </c>
       <c r="H46" s="27" t="inlineStr">
         <is>
-          <t>Fallback to Accts TransactionInquiry engages per design; result parity with primary path; fallback latency doesn't blow the window.</t>
+          <t>Fallback to Core TransactionInquiry engages per design; result parity with primary path; fallback latency doesn't blow the window.</t>
         </is>
       </c>
       <c r="I46" s="27" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="M47" s="27" t="inlineStr">
         <is>
-          <t>Latency SLIs per hop visible in APM-platform.</t>
+          <t>Latency SLIs per hop visible in Dynatrace.</t>
         </is>
       </c>
       <c r="N47" s="27" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>On-prem path loss (DX) — broker / onprem-broker / on-prem API GW</t>
+          <t>On-prem path loss (DX) — MBUS / GKP / on-prem API GW</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="F49" s="27" t="inlineStr">
         <is>
-          <t>broker clients, SVC-J (onprem-broker via service-mesh), REFDATA (on-prem API GW)</t>
+          <t>MBUS clients, TE (GKP via Envoy), MCC (on-prem API GW)</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>Each on-prem dependency fails per its class: Kafka per KFK-01; SVC-J's onprem-broker calls fail fast with degraded UX; REFDATA serves from local store/S3 config without on-prem GW.</t>
+          <t>Each on-prem dependency fails per its class: Kafka per KFK-01; TE's GKP calls fail fast with degraded UX; MCC serves from local store/S3 config without on-prem GW.</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="K49" s="27" t="inlineStr">
         <is>
-          <t>SVC-J hard-down</t>
+          <t>TE hard-down</t>
         </is>
       </c>
       <c r="L49" s="27" t="inlineStr">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="F52" s="27" t="inlineStr">
         <is>
-          <t>Long-call paths; SVC-G external→internal NLB pair</t>
+          <t>Long-call paths; DSM external→internal NLB pair</t>
         </is>
       </c>
       <c r="G52" s="27" t="inlineStr">
         <is>
-          <t>Hold connections idle past 350s; observe RST-on-next-byte semantics through the double-NLB SVC-G path.</t>
+          <t>Hold connections idle past 350s; observe RST-on-next-byte semantics through the double-NLB DSM path.</t>
         </is>
       </c>
       <c r="H52" s="27" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>edge-proxy path degradation (3-active edges)</t>
+          <t>DPS Proxy path degradation (3-active edges)</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>SVC-J, SVC-I, SVC-H</t>
+          <t>TE, CHE, SSE</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>Degrade one region's edge-proxy-Proxy-fronted path (latency/errors upstream of R53).</t>
+          <t>Degrade one region's DPS-Proxy-fronted path (latency/errors upstream of R53).</t>
         </is>
       </c>
       <c r="H55" s="27" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="O55" s="27" t="inlineStr">
         <is>
-          <t>us-west-2 presence + edge-proxy parity in PERF TBC (Open Items).</t>
+          <t>us-west-2 presence + DPS Proxy parity in PERF TBC (Open Items).</t>
         </is>
       </c>
       <c r="P55" s="27" t="n">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="B56" s="27" t="inlineStr">
         <is>
-          <t>SVC-E direct path (no API GW) exposure check</t>
+          <t>DLAT direct path (no API GW) exposure check</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="F56" s="27" t="inlineStr">
         <is>
-          <t>SVC-E</t>
+          <t>DLAT</t>
         </is>
       </c>
       <c r="G56" s="27" t="inlineStr">
         <is>
-          <t>Exercise SVC-E's R53→NLB→ALB path under fault (latency, auth anomalies).</t>
+          <t>Exercise DLAT's R53→NLB→ALB path under fault (latency, auth anomalies).</t>
         </is>
       </c>
       <c r="H56" s="27" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="J56" s="27" t="inlineStr">
         <is>
-          <t>SVC-E</t>
+          <t>DLAT</t>
         </is>
       </c>
       <c r="K56" s="27" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L56" s="27" t="inlineStr">
         <is>
-          <t>Control gap analysis complete (feeds SVC-E documentation gap).</t>
+          <t>Control gap analysis complete (feeds DLAT documentation gap).</t>
         </is>
       </c>
       <c r="M56" s="27" t="inlineStr">
         <is>
-          <t>SVC-E traffic observable at all (suspected gap).</t>
+          <t>DLAT traffic observable at all (suspected gap).</t>
         </is>
       </c>
       <c r="N56" s="27" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>EXT Posting 5xx burst</t>
+          <t>CBS Posting 5xx burst</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>SVC-D, SVC-L, SVC-P corrections</t>
+          <t>AFM, DCM, DTR corrections</t>
         </is>
       </c>
       <c r="G57" s="27" t="inlineStr">
         <is>
-          <t>Inject 5xx from EXT Posting via proxy layer in front of dedicated PERF EXT instance.</t>
+          <t>Inject 5xx from CBS Posting via proxy layer in front of dedicated PERF CBS instance.</t>
         </is>
       </c>
       <c r="H57" s="27" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="I57" s="27" t="inlineStr">
         <is>
-          <t>Toxiproxy/injection proxy (PERF EXT is live — cannot be failed itself)</t>
+          <t>Toxiproxy/injection proxy (PERF CBS is live — cannot be failed itself)</t>
         </is>
       </c>
       <c r="J57" s="27" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="M57" s="27" t="inlineStr">
         <is>
-          <t>EXT-Posting health as seen FROM Core alarmed (not just EXT's own monitoring).</t>
+          <t>CBS-Posting health as seen FROM Core alarmed (not just CBS's own monitoring).</t>
         </is>
       </c>
       <c r="N57" s="27" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="O57" s="27" t="inlineStr">
         <is>
-          <t>Dedicated PERF EXT: inject in front, never break the instance.</t>
+          <t>Dedicated PERF CBS: inject in front, never break the instance.</t>
         </is>
       </c>
       <c r="P57" s="27" t="n">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="B58" s="27" t="inlineStr">
         <is>
-          <t>EXT slow-but-alive (gray failure)</t>
+          <t>CBS slow-but-alive (gray failure)</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="F58" s="27" t="inlineStr">
         <is>
-          <t>SVC-D, SVC-G, SVC-L (EXT callers)</t>
+          <t>AFM, DSM, DCM (CBS callers)</t>
         </is>
       </c>
       <c r="G58" s="27" t="inlineStr">
         <is>
-          <t>Inject 5–15s latency (no errors) on EXT responses.</t>
+          <t>Inject 5–15s latency (no errors) on CBS responses.</t>
         </is>
       </c>
       <c r="H58" s="27" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="J58" s="27" t="inlineStr">
         <is>
-          <t>EXT callers</t>
+          <t>CBS callers</t>
         </is>
       </c>
       <c r="K58" s="27" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>EXT event stream stall</t>
+          <t>CBS event stream stall</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>SVC-M, SVC-N</t>
+          <t>DBE, DTE</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
         <is>
-          <t>Suppress EXT Balance/Transaction events (consumers healthy, topic silent).</t>
+          <t>Suppress CBS Balance/Transaction events (consumers healthy, topic silent).</t>
         </is>
       </c>
       <c r="H59" s="27" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="L59" s="27" t="inlineStr">
         <is>
-          <t>Staleness of enriched data downstream (EXT-3/SVC-R) bounded + alarmed.</t>
+          <t>Staleness of enriched data downstream (AU/ETU) bounded + alarmed.</t>
         </is>
       </c>
       <c r="M59" s="27" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>SVC-AD degradation</t>
+          <t>LCDP degradation</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="F60" s="27" t="inlineStr">
         <is>
-          <t>SVC-AD callers</t>
+          <t>LCDP callers</t>
         </is>
       </c>
       <c r="G60" s="27" t="inlineStr">
         <is>
-          <t>Inject errors/latency on SVC-AD calls.</t>
+          <t>Inject errors/latency on LCDP calls.</t>
         </is>
       </c>
       <c r="H60" s="27" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="J60" s="27" t="inlineStr">
         <is>
-          <t>SVC-AD callers</t>
+          <t>LCDP callers</t>
         </is>
       </c>
       <c r="K60" s="27" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="M60" s="27" t="inlineStr">
         <is>
-          <t>SVC-AD-as-seen-from-Core health visible.</t>
+          <t>LCDP-as-seen-from-Core health visible.</t>
         </is>
       </c>
       <c r="N60" s="27" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>EXT-3 / SVC-R unavailable (enriched-event downstream)</t>
+          <t>AU / ETU unavailable (enriched-event downstream)</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
@@ -8806,17 +8806,17 @@
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>SVC-M→EXT-3, SVC-N→SVC-R paths</t>
+          <t>DBE→AU, DTE→ETU paths</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
         <is>
-          <t>Block delivery of enriched events to EXT-3/SVC-R (Kafka-side or consumer-side per topology).</t>
+          <t>Block delivery of enriched events to AU/ETU (Kafka-side or consumer-side per topology).</t>
         </is>
       </c>
       <c r="H61" s="27" t="inlineStr">
         <is>
-          <t>Enriched events are durable in broker regardless of downstream health (pub/sub decoupling holds); no producer-side blocking.</t>
+          <t>Enriched events are durable in MBUS regardless of downstream health (pub/sub decoupling holds); no producer-side blocking.</t>
         </is>
       </c>
       <c r="I61" s="27" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>CUST failure — alert enrichment</t>
+          <t>CSU failure — alert enrichment</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
@@ -8912,17 +8912,17 @@
       </c>
       <c r="F62" s="27" t="inlineStr">
         <is>
-          <t>SVC-Q</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="G62" s="27" t="inlineStr">
         <is>
-          <t>Fail CUST (parent/child fetch) during alert processing.</t>
+          <t>Fail CSU (parent/child fetch) during alert processing.</t>
         </is>
       </c>
       <c r="H62" s="27" t="inlineStr">
         <is>
-          <t>SVC-Q degrades per design: alert sent without enrichment OR parked for cron recovery (its documented failure-recovery scheduler) — never silently dropped.</t>
+          <t>DAL degrades per design: alert sent without enrichment OR parked for cron recovery (its documented failure-recovery scheduler) — never silently dropped.</t>
         </is>
       </c>
       <c r="I62" s="27" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>context-service failure — SVC-J</t>
+          <t>ChannelContext failure — TE</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
@@ -9018,17 +9018,17 @@
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>SVC-J</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="G63" s="27" t="inlineStr">
         <is>
-          <t>Fail context-service calls from SVC-J.</t>
+          <t>Fail ChannelContext calls from TE.</t>
         </is>
       </c>
       <c r="H63" s="27" t="inlineStr">
         <is>
-          <t>SVC-J renders degraded-but-usable experience (partial data) rather than error page — BFF partial-failure rendering proven.</t>
+          <t>TE renders degraded-but-usable experience (partial data) rather than error page — BFF partial-failure rendering proven.</t>
         </is>
       </c>
       <c r="I63" s="27" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="J63" s="27" t="inlineStr">
         <is>
-          <t>SVC-J UX</t>
+          <t>TE UX</t>
         </is>
       </c>
       <c r="K63" s="27" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>feature-flag service flag evaluation unavailable</t>
+          <t>Split.io flag evaluation unavailable</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="G64" s="27" t="inlineStr">
         <is>
-          <t>Block feature-flag service from services.</t>
+          <t>Block Split.io from services.</t>
         </is>
       </c>
       <c r="H64" s="27" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>SSO-anywhere token issuance failure — SVC-J ingress</t>
+          <t>AuthAnywhere token issuance failure — TE ingress</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
@@ -9230,17 +9230,17 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>SVC-J (API GW token validate)</t>
+          <t>TE (API GW token validate)</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
         <is>
-          <t>Degrade SSO-anywhere validation path at SVC-J's edge.</t>
+          <t>Degrade AuthAnywhere validation path at TE's edge.</t>
         </is>
       </c>
       <c r="H65" s="27" t="inlineStr">
         <is>
-          <t>Existing sessions (cached validations) continue per TTL; new sessions fail with clean auth error; no retry storm against IdP.</t>
+          <t>Existing sessions (cached validations) continue per TTL; new sessions fail with clean auth error; no retry storm against IDP.</t>
         </is>
       </c>
       <c r="I65" s="27" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="J65" s="27" t="inlineStr">
         <is>
-          <t>SVC-J ingress auth</t>
+          <t>TE ingress auth</t>
         </is>
       </c>
       <c r="K65" s="27" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="O65" s="27" t="inlineStr">
         <is>
-          <t>IdP is shared platform — coordination required; scope to PERF path.</t>
+          <t>IDP is shared platform — coordination required; scope to PERF path.</t>
         </is>
       </c>
       <c r="P65" s="27" t="n">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="F66" s="27" t="inlineStr">
         <is>
-          <t>SVC-M (parameterstore reload strategy)</t>
+          <t>DBE (parameterstore reload strategy)</t>
         </is>
       </c>
       <c r="G66" s="27" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="J66" s="27" t="inlineStr">
         <is>
-          <t>SVC-M config</t>
+          <t>DBE config</t>
         </is>
       </c>
       <c r="K66" s="27" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="G67" s="27" t="inlineStr">
         <is>
-          <t>secrets-mgr/Secrets Manager outage window + force task recycles during it.</t>
+          <t>ASM/Secrets Manager outage window + force task recycles during it.</t>
         </is>
       </c>
       <c r="H67" s="27" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>app-folamdba orchestrated failover — full drill</t>
+          <t>dr-orchestrator orchestrated failover — full drill</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>app-folamdba + one APG scope</t>
+          <t>dr-orchestrator + one APG scope</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="O69" s="27" t="inlineStr">
         <is>
-          <t>app-folamdba PERF parity TBC (Open Items).</t>
+          <t>dr-orchestrator PERF parity TBC (Open Items).</t>
         </is>
       </c>
       <c r="P69" s="27" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="F70" s="27" t="inlineStr">
         <is>
-          <t>app-folamdba</t>
+          <t>dr-orchestrator</t>
         </is>
       </c>
       <c r="G70" s="27" t="inlineStr">
         <is>
-          <t>Fail app-folamdba mid-sequence (kill at defined steps).</t>
+          <t>Fail dr-orchestrator mid-sequence (kill at defined steps).</t>
         </is>
       </c>
       <c r="H70" s="27" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>APP-A, SVC-B</t>
+          <t>ALS, ARM</t>
         </is>
       </c>
       <c r="G71" s="27" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="F72" s="27" t="inlineStr">
         <is>
-          <t>SVC-J, SVC-I, SVC-H</t>
+          <t>TE, CHE, SSE</t>
         </is>
       </c>
       <c r="G72" s="27" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="O72" s="27" t="inlineStr">
         <is>
-          <t>us-west-2 presence in PERF TBC; SVC-H blocked on documentation.</t>
+          <t>us-west-2 presence in PERF TBC; SSE blocked on documentation.</t>
         </is>
       </c>
       <c r="P72" s="27" t="n">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>REFDATA Pilot Light activation</t>
+          <t>MCC Pilot Light activation</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
@@ -10098,17 +10098,17 @@
       </c>
       <c r="F73" s="27" t="inlineStr">
         <is>
-          <t>REFDATA</t>
+          <t>MCC</t>
         </is>
       </c>
       <c r="G73" s="27" t="inlineStr">
         <is>
-          <t>Activate REFDATA's pilot-light DR: stand up capacity, restore data path, cut over.</t>
+          <t>Activate MCC's pilot-light DR: stand up capacity, restore data path, cut over.</t>
         </is>
       </c>
       <c r="H73" s="27" t="inlineStr">
         <is>
-          <t>Activation runbook meets REFDATA's RTO; SVC-R scheduled pull resumes in DR region exactly once; S3 config current.</t>
+          <t>Activation runbook meets MCC's RTO; ETU scheduled pull resumes in DR region exactly once; S3 config current.</t>
         </is>
       </c>
       <c r="I73" s="27" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="J73" s="27" t="inlineStr">
         <is>
-          <t>REFDATA</t>
+          <t>MCC</t>
         </is>
       </c>
       <c r="K73" s="27" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="M73" s="27" t="inlineStr">
         <is>
-          <t>DR-region REFDATA monitored from cold start.</t>
+          <t>DR-region MCC monitored from cold start.</t>
         </is>
       </c>
       <c r="N73" s="27" t="inlineStr">
@@ -10204,17 +10204,17 @@
       </c>
       <c r="F74" s="27" t="inlineStr">
         <is>
-          <t>SVC-P</t>
+          <t>DTR</t>
         </is>
       </c>
       <c r="G74" s="27" t="inlineStr">
         <is>
-          <t>Execute regional failover while SVC-P is mid-run (cross-region S3 + bidirectional Aurora + regional Redis EOD cache).</t>
+          <t>Execute regional failover while DTR is mid-run (cross-region S3 + bidirectional Aurora + regional Redis EOD cache).</t>
         </is>
       </c>
       <c r="H74" s="27" t="inlineStr">
         <is>
-          <t>Recon state survives or safely restarts in DR region: S3 CRR current, Aurora consistent, Redis EOD cache REBUILT from EXT EOD API (it does not replicate).</t>
+          <t>Recon state survives or safely restarts in DR region: S3 CRR current, Aurora consistent, Redis EOD cache REBUILT from CBS EOD API (it does not replicate).</t>
         </is>
       </c>
       <c r="I74" s="27" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="F75" s="27" t="inlineStr">
         <is>
-          <t>SVC-J/SVC-I → SVC-C/SVC-D path</t>
+          <t>TE/CHE → SAM/AFM path</t>
         </is>
       </c>
       <c r="G75" s="27" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B76" s="27" t="inlineStr">
         <is>
-          <t>Detection baseline — APM-platform coverage &amp; latency</t>
+          <t>Detection baseline — Dynatrace coverage &amp; latency</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="H76" s="27" t="inlineStr">
         <is>
-          <t>APM-platform (SaaS) detects ≥ agreed % of injected faults within target latency with correct root-cause attribution — validating the 'not configured properly' concern with evidence.</t>
+          <t>Dynatrace (SaaS) detects ≥ agreed % of injected faults within target latency with correct root-cause attribution — validating the 'not configured properly' concern with evidence.</t>
         </is>
       </c>
       <c r="I76" s="27" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="O76" s="27" t="inlineStr">
         <is>
-          <t>APM-platform config should be env-agnostic — confirm same monitoring config deployed to PERF.</t>
+          <t>Dynatrace config should be env-agnostic — confirm same monitoring config deployed to PERF.</t>
         </is>
       </c>
       <c r="P76" s="27" t="n">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>CloudWatch alarm validation — app-folamdba triggers</t>
+          <t>CloudWatch alarm validation — dr-orchestrator triggers</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="F78" s="27" t="inlineStr">
         <is>
-          <t>SVC-O warmer stop; SVC-P purge skip; SVC-M reload block</t>
+          <t>DSC warmer stop; DTR purge skip; DBE reload block</t>
         </is>
       </c>
       <c r="G78" s="27" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="F80" s="27" t="inlineStr">
         <is>
-          <t>Each R4j-protected client (start: EXT clients)</t>
+          <t>Each R4j-protected client (start: CBS clients)</t>
         </is>
       </c>
       <c r="G80" s="27" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="F82" s="27" t="inlineStr">
         <is>
-          <t>Multi-hop path (edge→API→EXT)</t>
+          <t>Multi-hop path (edge→API→CBS)</t>
         </is>
       </c>
       <c r="G82" s="27" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="F86" s="27" t="inlineStr">
         <is>
-          <t>SVC-C + callers</t>
+          <t>SAM + callers</t>
         </is>
       </c>
       <c r="G86" s="27" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="F88" s="27" t="inlineStr">
         <is>
-          <t>Edge→SVC-D→EXT chain</t>
+          <t>Edge→AFM→CBS chain</t>
         </is>
       </c>
       <c r="G88" s="27" t="inlineStr">
         <is>
-          <t>EXT gray failure (EXT-02) + realistic edge traffic — watch the cascade attempt.</t>
+          <t>CBS gray failure (EXT-02) + realistic edge traffic — watch the cascade attempt.</t>
         </is>
       </c>
       <c r="H88" s="27" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="M88" s="27" t="inlineStr">
         <is>
-          <t>Cascade visible as coherent story in APM-platform.</t>
+          <t>Cascade visible as coherent story in Dynatrace.</t>
         </is>
       </c>
       <c r="N88" s="27" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>IdP platform outage — Kafka auth + API OAuth together</t>
+          <t>IDP platform outage — Kafka auth + API OAuth together</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="F89" s="27" t="inlineStr">
         <is>
-          <t>All IdP consumers</t>
+          <t>All IDP consumers</t>
         </is>
       </c>
       <c r="G89" s="27" t="inlineStr">
         <is>
-          <t>Simulate SSO-IdP unavailable: Kafka OAUTHBEARER (KFK-07) AND SVC-J ingress (EXT-09) simultaneously — IdP is a shared single point.</t>
+          <t>Simulate ADFS-IDP unavailable: Kafka OAUTHBEARER (KFK-07) AND TE ingress (EXT-09) simultaneously — IDP is a shared single point.</t>
         </is>
       </c>
       <c r="H89" s="27" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="L89" s="27" t="inlineStr">
         <is>
-          <t>IdP blast radius fully mapped — leadership-grade finding either way.</t>
+          <t>IDP blast radius fully mapped — leadership-grade finding either way.</t>
         </is>
       </c>
       <c r="M89" s="27" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="F91" s="27" t="inlineStr">
         <is>
-          <t>Full journey scope incl. app-folamdba, SVC-P</t>
+          <t>Full journey scope incl. dr-orchestrator, DTR</t>
         </is>
       </c>
       <c r="G91" s="27" t="inlineStr">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Detection baseline + contained singles + integrity logic (idempotency, dual-trigger, breaker both paths, timeout chain, SVC-G state, recon restart)</t>
+          <t>Detection baseline + contained singles + integrity logic (idempotency, dual-trigger, breaker both paths, timeout chain, DSM state, recon restart)</t>
         </is>
       </c>
       <c r="C2" s="27" t="inlineStr">
         <is>
-          <t>PERF load harness ready; FIS onboarded; APM-platform/CloudWatch access for evidence capture; game-day runbook + abort authority named.</t>
+          <t>PERF load harness ready; FIS onboarded; Dynatrace/CloudWatch access for evidence capture; game-day runbook + abort authority named.</t>
         </is>
       </c>
       <c r="D2" s="27" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>Wave-1 exit met; custom tooling built (Toxiproxy layer, IAM/KMS/secrets-mgr deny scripts, file injectors, event suppressors); FIS Fargate network actions confirmed or tc-fallback ready.</t>
+          <t>Wave-1 exit met; custom tooling built (Toxiproxy layer, IAM/KMS/ASM deny scripts, file injectors, event suppressors); FIS Fargate network actions confirmed or tc-fallback ready.</t>
         </is>
       </c>
       <c r="D3" s="27" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>Compound envelope evidence (failover-under-saturation, cascade containment, IdP blast radius); MTTD/MTTI baseline from drills.</t>
+          <t>Compound envelope evidence (failover-under-saturation, cascade containment, IDP blast radius); MTTD/MTTI baseline from drills.</t>
         </is>
       </c>
       <c r="E4" s="27">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>Waves 1–3 evidence pack; leadership sign-off; app-folamdba PERF parity confirmed; rollback/abort rehearsed.</t>
+          <t>Waves 1–3 evidence pack; leadership sign-off; dr-orchestrator PERF parity confirmed; rollback/abort rehearsed.</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="C2" s="27" t="inlineStr">
         <is>
-          <t>Diagram silence ≠ proof of direct connection (per your table's own caveat). CE-DB-01/02 asymmetry design assumes proxy = SVC-L/SVC-M/SVC-N only. Enrique checking.</t>
+          <t>Diagram silence ≠ proof of direct connection (per your table's own caveat). CE-DB-01/02 asymmetry design assumes proxy = DCM/DBE/DTE only. Enrique checking.</t>
         </is>
       </c>
       <c r="D2" s="27" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>APM-platform PERF config parity</t>
+          <t>Dynatrace PERF config parity</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>Formal list: task counts/scaling, Aurora instance classes, data volumes, us-west-2 presence for 3-Active tier, pilot-light infra for REFDATA, R53/DNS config, app-folamdba parity, timeout config parity. Every 'Medium/Low PERF validity' flag resolves against this register.</t>
+          <t>Formal list: task counts/scaling, Aurora instance classes, data volumes, us-west-2 presence for 3-Active tier, pilot-light infra for MCC, R53/DNS config, dr-orchestrator parity, timeout config parity. Every 'Medium/Low PERF validity' flag resolves against this register.</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>Decide and build the Toxiproxy (or equivalent) layer in front of dedicated PERF EXT + SVC-AD/CUST/context-service paths. PERF EXT is live — inject in front, never break it. Gates all CE-EXT.</t>
+          <t>Decide and build the Toxiproxy (or equivalent) layer in front of dedicated PERF CBS + LCDP/CSU/ChannelContext paths. PERF CBS is live — inject in front, never break it. Gates all CE-EXT.</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
@@ -13671,12 +13671,12 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Spend &amp; Save documentation</t>
+          <t>Spend-Track documentation</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>No artifact exists. All SVC-H scenarios blocked until minimum documentation lands. Finding in itself.</t>
+          <t>No artifact exists. All SSE scenarios blocked until minimum documentation lands. Finding in itself.</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>SVC-E dependency documentation</t>
+          <t>DLAT dependency documentation</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -13771,12 +13771,12 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>Recon reversibility in PERF EXT</t>
+          <t>Recon reversibility in PERF CBS</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>CE-PIPE-10 sends real Posting corrections to the dedicated PERF EXT — confirm test postings are reversible/isolated before executing.</t>
+          <t>CE-PIPE-10 sends real Posting corrections to the dedicated PERF CBS — confirm test postings are reversible/isolated before executing.</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
@@ -13885,7 +13885,7 @@
     <row r="8" ht="175.5" customHeight="1" s="19">
       <c r="A8" s="34" t="inlineStr">
         <is>
-          <t>•  Config sourced from Secrets Manager / Parameter Store / external-vault-style vaults (i.e., the key exists in code but the value is externally resolved) is EXTERNAL_CONFIG — not resolvable from repo. Do not attempt to guess the resolved value.</t>
+          <t>•  Config sourced from Secrets Manager / Parameter Store / VaultSM-ASM-style vaults (i.e., the key exists in code but the value is externally resolved) is EXTERNAL_CONFIG — not resolvable from repo. Do not attempt to guess the resolved value.</t>
         </is>
       </c>
     </row>
@@ -14355,12 +14355,12 @@
     <row r="14" ht="42.75" customHeight="1" s="19">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>template.yaml/json with AWSTemplateFormatVersion, or SVC-C's template.yaml</t>
+          <t>template.yaml/json with AWSTemplateFormatVersion, or SAM's template.yaml</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>CloudFormation / SVC-C</t>
+          <t>CloudFormation / SAM</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
